--- a/jira_export_2026-07-03.xlsx
+++ b/jira_export_2026-07-03.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>6,604 €</t>
+          <t>16,606 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>5,236 €</t>
+          <t>15,239 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>86 h</t>
+          <t>94 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -895,7 +895,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>252</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P118"/>
+  <dimension ref="A1:P130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1063,27 +1063,27 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34337</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t>[Commune de Chalons-sur-Saone] - Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>Commune de Chalons-sur-Saone</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t>Achat nouveau PAX A920</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J5" s="12" t="n">
@@ -1114,16 +1114,16 @@
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34258</t>
+          <t>PDMDEP-34345</t>
         </is>
       </c>
       <c r="M5" s="12" t="inlineStr">
         <is>
-          <t>00171361</t>
+          <t>00171711</t>
         </is>
       </c>
       <c r="N5" s="13" t="n">
-        <v>2127.2</v>
+        <v>450</v>
       </c>
       <c r="O5" s="14" t="n">
         <v>0</v>
@@ -1135,32 +1135,32 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
@@ -1170,34 +1170,34 @@
       </c>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L6" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N6" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="17" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="O6" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P6" s="17" t="n">
@@ -1207,27 +1207,27 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1247,29 +1247,29 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J7" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M7" s="12" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13" t="n">
+        <v>2127.2</v>
+      </c>
+      <c r="O7" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="13" t="n">
@@ -1279,32 +1279,32 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -1314,64 +1314,64 @@
       </c>
       <c r="H8" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J8" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N8" s="17" t="n">
-        <v>3207.7</v>
+        <v>0</v>
       </c>
       <c r="O8" s="17" t="n">
-        <v>3207.7</v>
+        <v>0</v>
       </c>
       <c r="P8" s="17" t="n">
-        <v>2138.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -1391,27 +1391,27 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J9" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M9" s="12" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N9" s="13" t="n">
-        <v>353.5</v>
+        <v>350</v>
       </c>
       <c r="O9" s="14" t="n">
         <v>0</v>
@@ -1423,27 +1423,27 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="H10" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J10" s="16" t="n">
@@ -1474,16 +1474,16 @@
       </c>
       <c r="L10" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N10" s="17" t="n">
-        <v>1242.5</v>
+        <v>554</v>
       </c>
       <c r="O10" s="14" t="n">
         <v>0</v>
@@ -1495,12 +1495,12 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -1530,69 +1530,69 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J11" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M11" s="12" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N11" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="O11" s="14" t="n">
-        <v>0</v>
+        <v>3207.7</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>3207.7</v>
       </c>
       <c r="P11" s="13" t="n">
-        <v>0</v>
+        <v>2138.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-34147</t>
         </is>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert</t>
+          <t>[Mairie de Vaison la romaine] - Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>Mairie de Vaison la romaine</t>
         </is>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Ajout d'une régie et mise en place de deux PAX</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -1607,29 +1607,29 @@
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J12" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L12" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-34155</t>
         </is>
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00171080</t>
         </is>
       </c>
       <c r="N12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17" t="n">
+        <v>848.7</v>
+      </c>
+      <c r="O12" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="17" t="n">
@@ -1639,12 +1639,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1679,27 +1679,27 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J13" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M13" s="12" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N13" s="13" t="n">
-        <v>2100</v>
+        <v>353.5</v>
       </c>
       <c r="O13" s="14" t="n">
         <v>0</v>
@@ -1711,27 +1711,27 @@
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -1751,64 +1751,64 @@
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J14" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M14" s="16" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N14" s="17" t="n">
-        <v>340</v>
-      </c>
-      <c r="O14" s="17" t="n">
-        <v>340</v>
+        <v>1242.5</v>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P14" s="17" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1823,64 +1823,64 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M15" s="12" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N15" s="13" t="n">
-        <v>657.3</v>
+        <v>280</v>
       </c>
       <c r="O15" s="14" t="n">
-        <v>219.1</v>
+        <v>0</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>175.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-34045</t>
         </is>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[COMMUNE DE NEUILLY SUR MARNE] - Migration GEODP PLACIER</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE NEUILLY SUR MARNE</t>
         </is>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Migration GEODP PLACIER</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H16" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J16" s="16" t="n">
@@ -1906,16 +1906,16 @@
       </c>
       <c r="L16" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-34054</t>
         </is>
       </c>
       <c r="M16" s="16" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00170461</t>
         </is>
       </c>
       <c r="N16" s="17" t="n">
-        <v>1890</v>
+        <v>850</v>
       </c>
       <c r="O16" s="14" t="n">
         <v>0</v>
@@ -1927,12 +1927,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1967,23 +1967,23 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J17" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M17" s="12" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N17" s="13" t="n">
@@ -1999,27 +1999,27 @@
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33755</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
-          <t>Quentin BORDILLON</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MAINTENON</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
@@ -2039,27 +2039,27 @@
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J18" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L18" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33764</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M18" s="16" t="inlineStr">
         <is>
-          <t>00169558</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N18" s="17" t="n">
-        <v>1365</v>
+        <v>2100</v>
       </c>
       <c r="O18" s="14" t="n">
         <v>0</v>
@@ -2071,32 +2071,32 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -2106,49 +2106,49 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J19" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L19" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M19" s="12" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N19" s="13" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="P19" s="13" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -2158,12 +2158,12 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -2183,44 +2183,44 @@
       </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J20" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="16" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L20" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M20" s="16" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17" t="n">
-        <v>0</v>
+        <v>657.3</v>
+      </c>
+      <c r="O20" s="14" t="n">
+        <v>219.1</v>
       </c>
       <c r="P20" s="17" t="n">
-        <v>0</v>
+        <v>175.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2255,27 +2255,27 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33724</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M21" s="12" t="inlineStr">
         <is>
-          <t>00169462</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N21" s="13" t="n">
-        <v>1000</v>
+        <v>1890</v>
       </c>
       <c r="O21" s="14" t="n">
         <v>0</v>
@@ -2287,32 +2287,32 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33686</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>EUROMETROPOLE DE METZ</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>Paiement CB + 3 PAX</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
@@ -2327,29 +2327,29 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J22" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33694</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M22" s="16" t="inlineStr">
         <is>
-          <t>00169321</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N22" s="17" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="17" t="n">
@@ -2359,12 +2359,12 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33755</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
+          <t>[COMMUNE DE MAINTENON] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MAINTENON</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
@@ -2410,16 +2410,16 @@
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33764</t>
         </is>
       </c>
       <c r="M23" s="12" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169558</t>
         </is>
       </c>
       <c r="N23" s="13" t="n">
-        <v>4040</v>
+        <v>1365</v>
       </c>
       <c r="O23" s="14" t="n">
         <v>0</v>
@@ -2431,27 +2431,27 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33566</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] Flux WFS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Flux WFS (PS)</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -2471,29 +2471,29 @@
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J24" s="16" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L24" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33570</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M24" s="16" t="inlineStr">
         <is>
-          <t>00168466</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N24" s="17" t="n">
-        <v>895</v>
-      </c>
-      <c r="O24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P24" s="17" t="n">
@@ -2503,32 +2503,32 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>MM - Up - GeODP - PAX</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -2543,29 +2543,29 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33561</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M25" s="12" t="inlineStr">
         <is>
-          <t>00168460</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N25" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="13" t="n">
@@ -2575,32 +2575,32 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>PRESTA PURGE DES ACTES EN URGENCE</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
@@ -2610,32 +2610,32 @@
       </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J26" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L26" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33724</t>
         </is>
       </c>
       <c r="M26" s="16" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00169462</t>
         </is>
       </c>
       <c r="N26" s="17" t="n">
-        <v>1416</v>
+        <v>1000</v>
       </c>
       <c r="O26" s="14" t="n">
         <v>0</v>
@@ -2647,32 +2647,32 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33686</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[EUROMETROPOLE DE METZ] - Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>EUROMETROPOLE DE METZ</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Paiement CB + 3 PAX</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -2687,27 +2687,27 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33694</t>
         </is>
       </c>
       <c r="M27" s="12" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169321</t>
         </is>
       </c>
       <c r="N27" s="13" t="n">
-        <v>171.4</v>
+        <v>1500</v>
       </c>
       <c r="O27" s="14" t="n">
         <v>0</v>
@@ -2719,27 +2719,27 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33461</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Quentin BORDILLON</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Mairie de Buis-les-baronnies</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>INITIATION GEODP</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -2754,32 +2754,32 @@
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J28" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K28" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33465</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>00167986</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N28" s="17" t="n">
-        <v>450</v>
+        <v>4040</v>
       </c>
       <c r="O28" s="14" t="n">
         <v>0</v>
@@ -2791,32 +2791,32 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J29" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="13" t="n">
+        <v>407</v>
+      </c>
+      <c r="O29" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="13" t="n">
@@ -2863,32 +2863,32 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33566</t>
         </is>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
+          <t>[COMMUNE DE LILLE] Flux WFS</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>MM - Up - LiExp - Flux WFS (PS)</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
@@ -2898,32 +2898,32 @@
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J30" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" s="16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L30" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33570</t>
         </is>
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00168466</t>
         </is>
       </c>
       <c r="N30" s="17" t="n">
-        <v>417.4</v>
+        <v>895</v>
       </c>
       <c r="O30" s="14" t="n">
         <v>0</v>
@@ -2935,32 +2935,32 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t>MM - Up - GeODP - PAX</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -2975,93 +2975,101 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="J31" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33561</t>
         </is>
       </c>
       <c r="M31" s="12" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00168460</t>
         </is>
       </c>
       <c r="N31" s="13" t="n">
-        <v>617.04</v>
-      </c>
-      <c r="O31" s="13" t="n">
-        <v>1028.4</v>
+        <v>500</v>
+      </c>
+      <c r="O31" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P31" s="13" t="n">
-        <v>1371.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33363</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>MM - Up - LiExp - Vérif</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J32" s="16" t="n">
         <v>2</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L32" s="16" t="inlineStr"/>
-      <c r="M32" s="16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-33526</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>00168179</t>
+        </is>
+      </c>
       <c r="N32" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="17" t="n">
+        <v>1416</v>
+      </c>
+      <c r="O32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="17" t="n">
@@ -3071,12 +3079,12 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33348</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
@@ -3086,12 +3094,12 @@
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modélisation + Modif Marianne </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -3111,7 +3119,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J33" s="12" t="n">
@@ -3122,12 +3130,12 @@
       </c>
       <c r="L33" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33352</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M33" s="12" t="inlineStr">
         <is>
-          <t>00167402</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N33" s="13" t="n">
@@ -3143,32 +3151,32 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33461</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t>[Mairie de Buis-les-baronnies] - INITIATION GEODP</t>
         </is>
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>Mairie de Buis-les-baronnies</t>
         </is>
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>INITIATION GEODP</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
@@ -3183,27 +3191,27 @@
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J34" s="16" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L34" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33465</t>
         </is>
       </c>
       <c r="M34" s="16" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00167986</t>
         </is>
       </c>
       <c r="N34" s="17" t="n">
-        <v>625</v>
+        <v>450</v>
       </c>
       <c r="O34" s="14" t="n">
         <v>0</v>
@@ -3215,27 +3223,27 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -3255,7 +3263,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J35" s="12" t="n">
@@ -3266,18 +3274,18 @@
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M35" s="12" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N35" s="13" t="n">
-        <v>600</v>
-      </c>
-      <c r="O35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="13" t="n">
@@ -3287,12 +3295,12 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES ] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C36" s="16" t="inlineStr">
@@ -3302,12 +3310,12 @@
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -3327,59 +3335,59 @@
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J36" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="L36" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N36" s="17" t="n">
-        <v>1618.5</v>
+        <v>417.4</v>
       </c>
       <c r="O36" s="17" t="n">
-        <v>1618.5</v>
+        <v>1252.2</v>
       </c>
       <c r="P36" s="17" t="n">
-        <v>462.43</v>
+        <v>834.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -3399,97 +3407,89 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J37" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M37" s="12" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O37" s="14" t="n">
-        <v>0</v>
+        <v>617.04</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>1028.4</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>0</v>
+        <v>1371.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-33363</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[AMIENS METROPOLE] LiExp - Vérif</t>
         </is>
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>MM - Up - LiExp - Vérif</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="J38" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L38" s="16" t="inlineStr">
-        <is>
-          <t>PDMDEP-32974</t>
-        </is>
-      </c>
-      <c r="M38" s="16" t="inlineStr">
-        <is>
-          <t>00165260</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="16" t="inlineStr"/>
+      <c r="M38" s="16" t="inlineStr"/>
       <c r="N38" s="17" t="n">
         <v>0</v>
       </c>
@@ -3503,32 +3503,32 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32848</t>
+          <t>PDMDEP-33348</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
+          <t xml:space="preserve">[MAISONS ALFORT] - Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRENOBLE</t>
+          <t xml:space="preserve">COMMUNE DE MAISONS ALFORT </t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Modification modèles de facture</t>
+          <t xml:space="preserve">Modélisation + Modif Marianne </t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -3543,27 +3543,27 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="J39" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32852</t>
+          <t>PDMDEP-33352</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
         <is>
-          <t>00164564</t>
+          <t>00167402</t>
         </is>
       </c>
       <c r="N39" s="13" t="n">
-        <v>300</v>
+        <v>171.4</v>
       </c>
       <c r="O39" s="14" t="n">
         <v>0</v>
@@ -3575,27 +3575,27 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -3610,32 +3610,32 @@
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J40" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M40" s="16" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N40" s="17" t="n">
-        <v>900</v>
+        <v>149</v>
       </c>
       <c r="O40" s="14" t="n">
         <v>0</v>
@@ -3647,27 +3647,27 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -3687,27 +3687,27 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M41" s="12" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N41" s="13" t="n">
-        <v>705</v>
+        <v>625</v>
       </c>
       <c r="O41" s="14" t="n">
         <v>0</v>
@@ -3719,27 +3719,27 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - Crédits 21 heures (3j)</t>
         </is>
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -3759,27 +3759,27 @@
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J42" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K42" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L42" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N42" s="17" t="n">
-        <v>564</v>
+        <v>600</v>
       </c>
       <c r="O42" s="14" t="n">
         <v>0</v>
@@ -3791,12 +3791,12 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J43" s="12" t="n">
@@ -3842,16 +3842,16 @@
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
-        <v>2138.2</v>
+        <v>3621</v>
       </c>
       <c r="O43" s="14" t="n">
         <v>0</v>
@@ -3863,27 +3863,27 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -3903,59 +3903,59 @@
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J44" s="16" t="n">
         <v>3</v>
       </c>
       <c r="K44" s="16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N44" s="17" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="O44" s="14" t="n">
-        <v>0</v>
+        <v>1618.5</v>
+      </c>
+      <c r="O44" s="17" t="n">
+        <v>1618.5</v>
       </c>
       <c r="P44" s="17" t="n">
-        <v>0</v>
+        <v>462.43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3975,27 +3975,27 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
-        <v>548.4</v>
+        <v>1000</v>
       </c>
       <c r="O45" s="14" t="n">
         <v>0</v>
@@ -4007,12 +4007,12 @@
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -4042,34 +4042,34 @@
       </c>
       <c r="H46" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J46" s="16" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L46" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M46" s="16" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N46" s="17" t="n">
-        <v>552</v>
-      </c>
-      <c r="O46" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P46" s="17" t="n">
@@ -4079,32 +4079,32 @@
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32848</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE GRENOBLE] - Modification modèles de facture</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE GRENOBLE</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Modification modèles de facture</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
@@ -4130,16 +4130,16 @@
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32852</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00164564</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>142.1</v>
+        <v>300</v>
       </c>
       <c r="O47" s="14" t="n">
         <v>0</v>
@@ -4151,12 +4151,12 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32831</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE PANTIN</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -4186,32 +4186,32 @@
       </c>
       <c r="H48" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="J48" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" s="16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32837</t>
         </is>
       </c>
       <c r="M48" s="16" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00164275</t>
         </is>
       </c>
       <c r="N48" s="17" t="n">
-        <v>1868</v>
+        <v>900</v>
       </c>
       <c r="O48" s="14" t="n">
         <v>0</v>
@@ -4223,27 +4223,27 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4263,27 +4263,27 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N49" s="13" t="n">
-        <v>882.5</v>
+        <v>705</v>
       </c>
       <c r="O49" s="14" t="n">
         <v>0</v>
@@ -4295,12 +4295,12 @@
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
@@ -4335,29 +4335,29 @@
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J50" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M50" s="16" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N50" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="17" t="n">
+        <v>564</v>
+      </c>
+      <c r="O50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="17" t="n">
@@ -4367,12 +4367,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4402,69 +4402,69 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>450</v>
+        <v>2138.2</v>
       </c>
       <c r="O51" s="14" t="n">
-        <v>0</v>
+        <v>1375.2</v>
       </c>
       <c r="P51" s="13" t="n">
-        <v>0</v>
+        <v>392.91</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
@@ -4474,32 +4474,32 @@
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J52" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N52" s="17" t="n">
-        <v>1046.5</v>
+        <v>283.5</v>
       </c>
       <c r="O52" s="14" t="n">
         <v>0</v>
@@ -4511,32 +4511,32 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -4546,32 +4546,32 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J53" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>250</v>
+        <v>548.4</v>
       </c>
       <c r="O53" s="14" t="n">
         <v>0</v>
@@ -4583,12 +4583,12 @@
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
@@ -4623,27 +4623,27 @@
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J54" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N54" s="17" t="n">
-        <v>407</v>
+        <v>552</v>
       </c>
       <c r="O54" s="14" t="n">
         <v>0</v>
@@ -4655,27 +4655,27 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -4690,32 +4690,32 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>440.38</v>
+        <v>142.1</v>
       </c>
       <c r="O55" s="14" t="n">
         <v>0</v>
@@ -4727,27 +4727,27 @@
     <row r="56">
       <c r="A56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J56" s="16" t="n">
         <v>4</v>
       </c>
       <c r="K56" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N56" s="17" t="n">
-        <v>285</v>
+        <v>1868</v>
       </c>
       <c r="O56" s="14" t="n">
         <v>0</v>
@@ -4799,12 +4799,12 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
@@ -4850,16 +4850,16 @@
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>1325</v>
+        <v>882.5</v>
       </c>
       <c r="O57" s="14" t="n">
         <v>0</v>
@@ -4871,27 +4871,27 @@
     <row r="58">
       <c r="A58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
@@ -4911,30 +4911,30 @@
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J58" s="16" t="n">
         <v>4</v>
       </c>
       <c r="K58" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M58" s="16" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N58" s="17" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="O58" s="17" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="P58" s="17" t="n">
         <v>0</v>
@@ -4943,27 +4943,27 @@
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -4978,12 +4978,12 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
@@ -4994,16 +4994,16 @@
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="O59" s="14" t="n">
         <v>0</v>
@@ -5015,32 +5015,32 @@
     <row r="60">
       <c r="A60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="H60" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J60" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K60" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M60" s="16" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N60" s="17" t="n">
-        <v>203.5</v>
+        <v>1046.5</v>
       </c>
       <c r="O60" s="14" t="n">
         <v>0</v>
@@ -5087,27 +5087,27 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -5127,27 +5127,27 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>150</v>
+        <v>765</v>
       </c>
       <c r="O61" s="14" t="n">
         <v>0</v>
@@ -5159,32 +5159,32 @@
     <row r="62">
       <c r="A62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
@@ -5194,34 +5194,34 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J62" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K62" s="16" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L62" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M62" s="16" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N62" s="17" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O62" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="17" t="n">
@@ -5231,61 +5231,69 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J63" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L63" s="12" t="inlineStr"/>
-      <c r="M63" s="12" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-32095</t>
+        </is>
+      </c>
+      <c r="M63" s="12" t="inlineStr">
+        <is>
+          <t>00160474</t>
+        </is>
+      </c>
       <c r="N63" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="13" t="n">
+        <v>407</v>
+      </c>
+      <c r="O63" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="13" t="n">
@@ -5295,12 +5303,12 @@
     <row r="64">
       <c r="A64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
@@ -5310,12 +5318,12 @@
       </c>
       <c r="D64" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
@@ -5335,29 +5343,29 @@
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J64" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L64" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M64" s="16" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="17" t="n">
+        <v>257.15</v>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="17" t="n">
@@ -5367,27 +5375,27 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -5402,34 +5410,34 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="13" t="n">
+        <v>440.38</v>
+      </c>
+      <c r="O65" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P65" s="13" t="n">
@@ -5439,12 +5447,12 @@
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
@@ -5454,12 +5462,12 @@
       </c>
       <c r="D66" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
@@ -5474,32 +5482,32 @@
       </c>
       <c r="H66" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J66" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M66" s="16" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N66" s="17" t="n">
-        <v>210</v>
+        <v>285</v>
       </c>
       <c r="O66" s="14" t="n">
         <v>0</v>
@@ -5511,27 +5519,27 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31285</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Valentin CAUJOLLE</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5551,27 +5559,27 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>16/02/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31289</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M67" s="12" t="inlineStr">
         <is>
-          <t>00156834</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>71.2</v>
+        <v>1325</v>
       </c>
       <c r="O67" s="14" t="n">
         <v>0</v>
@@ -5583,32 +5591,32 @@
     <row r="68">
       <c r="A68" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G68" s="16" t="inlineStr">
@@ -5618,35 +5626,35 @@
       </c>
       <c r="H68" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J68" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M68" s="16" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N68" s="17" t="n">
-        <v>130</v>
-      </c>
-      <c r="O68" s="14" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O68" s="17" t="n">
+        <v>120</v>
       </c>
       <c r="P68" s="17" t="n">
         <v>0</v>
@@ -5655,27 +5663,27 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -5690,32 +5698,32 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>255</v>
+        <v>45</v>
       </c>
       <c r="O69" s="14" t="n">
         <v>0</v>
@@ -5727,12 +5735,12 @@
     <row r="70">
       <c r="A70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
@@ -5742,7 +5750,7 @@
       </c>
       <c r="D70" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E70" s="16" t="inlineStr">
@@ -5767,27 +5775,27 @@
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J70" s="16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M70" s="16" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N70" s="17" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="O70" s="14" t="n">
         <v>0</v>
@@ -5799,27 +5807,27 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -5834,32 +5842,32 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>140</v>
+        <v>203.5</v>
       </c>
       <c r="O71" s="14" t="n">
         <v>0</v>
@@ -5871,32 +5879,32 @@
     <row r="72">
       <c r="A72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F72" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="16" t="inlineStr">
@@ -5906,32 +5914,32 @@
       </c>
       <c r="H72" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J72" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K72" s="16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L72" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M72" s="16" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N72" s="17" t="n">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="O72" s="14" t="n">
         <v>0</v>
@@ -5943,27 +5951,27 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -5973,7 +5981,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -5983,25 +5991,17 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L73" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-30197</t>
-        </is>
-      </c>
-      <c r="M73" s="12" t="inlineStr">
-        <is>
-          <t>00153939</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L73" s="12" t="inlineStr"/>
+      <c r="M73" s="12" t="inlineStr"/>
       <c r="N73" s="13" t="n">
         <v>0</v>
       </c>
@@ -6015,32 +6015,32 @@
     <row r="74">
       <c r="A74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F74" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="16" t="inlineStr">
@@ -6050,34 +6050,34 @@
       </c>
       <c r="H74" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J74" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K74" s="16" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L74" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M74" s="16" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N74" s="17" t="n">
-        <v>350</v>
-      </c>
-      <c r="O74" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="17" t="n">
@@ -6087,12 +6087,12 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6127,23 +6127,23 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
@@ -6159,32 +6159,32 @@
     <row r="76">
       <c r="A76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E76" s="16" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F76" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="16" t="inlineStr">
@@ -6194,34 +6194,34 @@
       </c>
       <c r="H76" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J76" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K76" s="16" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="L76" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M76" s="16" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N76" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="O76" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="17" t="n">
@@ -6231,27 +6231,27 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31285</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE LUNEL] - FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Valentin CAUJOLLE</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>FDS pour Littéralis Expert. Déjà chiffré en amont dans le ticket 1333</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -6271,29 +6271,29 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/02/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-31289</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00156834</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="O77" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="13" t="n">
@@ -6303,32 +6303,32 @@
     <row r="78">
       <c r="A78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F78" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="16" t="inlineStr">
@@ -6338,34 +6338,34 @@
       </c>
       <c r="H78" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J78" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K78" s="16" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="L78" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M78" s="16" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N78" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="O78" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P78" s="17" t="n">
@@ -6375,30 +6375,32 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Migration V2 classique + abo CB</t>
+        </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6408,32 +6410,32 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>157.5</v>
+        <v>255</v>
       </c>
       <c r="O79" s="14" t="n">
         <v>0</v>
@@ -6445,30 +6447,32 @@
     <row r="80">
       <c r="A80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v/>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
       </c>
       <c r="F80" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="16" t="inlineStr">
@@ -6478,32 +6482,32 @@
       </c>
       <c r="H80" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J80" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M80" s="16" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N80" s="17" t="n">
-        <v>2812.32</v>
+        <v>1000</v>
       </c>
       <c r="O80" s="14" t="n">
         <v>0</v>
@@ -6515,32 +6519,32 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6550,32 +6554,32 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>392.5</v>
+        <v>140</v>
       </c>
       <c r="O81" s="14" t="n">
         <v>0</v>
@@ -6587,32 +6591,32 @@
     <row r="82">
       <c r="A82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D82" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F82" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="16" t="inlineStr">
@@ -6622,32 +6626,32 @@
       </c>
       <c r="H82" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J82" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K82" s="16" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="L82" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M82" s="16" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N82" s="17" t="n">
-        <v>1556.25</v>
+        <v>200</v>
       </c>
       <c r="O82" s="14" t="n">
         <v>0</v>
@@ -6659,12 +6663,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6674,12 +6678,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6694,34 +6698,34 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O83" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
@@ -6731,12 +6735,12 @@
     <row r="84">
       <c r="A84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C84" s="16" t="inlineStr">
@@ -6746,12 +6750,12 @@
       </c>
       <c r="D84" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr">
@@ -6766,34 +6770,34 @@
       </c>
       <c r="H84" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J84" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K84" s="16" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="L84" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M84" s="16" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N84" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O84" s="17" t="n">
+        <v>350</v>
+      </c>
+      <c r="O84" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P84" s="17" t="n">
@@ -6803,27 +6807,27 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6838,28 +6842,28 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0.45</v>
+        <v>1.75</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
@@ -6875,26 +6879,28 @@
     <row r="86">
       <c r="A86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
         <is>
@@ -6913,23 +6919,23 @@
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J86" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K86" s="16" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L86" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M86" s="16" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N86" s="17" t="n">
@@ -6945,26 +6951,28 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E87" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
@@ -6978,34 +6986,34 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>2.5</v>
+        <v>0.25</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>732</v>
-      </c>
-      <c r="O87" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
@@ -7015,12 +7023,12 @@
     <row r="88">
       <c r="A88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C88" s="16" t="inlineStr">
@@ -7030,12 +7038,12 @@
       </c>
       <c r="D88" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>Déploiement LiEx</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr">
@@ -7050,28 +7058,28 @@
       </c>
       <c r="H88" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J88" s="16" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K88" s="16" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L88" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M88" s="16" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N88" s="17" t="n">
@@ -7087,12 +7095,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7102,7 +7110,7 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E89" s="12" t="n">
@@ -7120,32 +7128,32 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>1212</v>
+        <v>157.5</v>
       </c>
       <c r="O89" s="14" t="n">
         <v>0</v>
@@ -7157,12 +7165,12 @@
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C90" s="16" t="inlineStr">
@@ -7172,7 +7180,7 @@
       </c>
       <c r="D90" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="E90" s="16" t="n">
@@ -7190,34 +7198,34 @@
       </c>
       <c r="H90" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I90" s="16" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J90" s="16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K90" s="16" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M90" s="16" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N90" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="17" t="n">
+        <v>2812.32</v>
+      </c>
+      <c r="O90" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="17" t="n">
@@ -7227,26 +7235,28 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
-        </is>
-      </c>
-      <c r="E91" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
@@ -7260,34 +7270,34 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="13" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="O91" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="13" t="n">
@@ -7297,26 +7307,28 @@
     <row r="92">
       <c r="A92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C92" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="16" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E92" s="16" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F92" s="16" t="inlineStr">
         <is>
@@ -7335,29 +7347,29 @@
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J92" s="16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K92" s="16" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="L92" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M92" s="16" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N92" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="17" t="n">
+        <v>1556.25</v>
+      </c>
+      <c r="O92" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="17" t="n">
@@ -7367,26 +7379,28 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E93" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
@@ -7405,29 +7419,29 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O93" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7437,12 +7451,12 @@
     <row r="94">
       <c r="A94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C94" s="16" t="inlineStr">
@@ -7452,11 +7466,13 @@
       </c>
       <c r="D94" s="16" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
-        </is>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F94" s="16" t="inlineStr">
         <is>
@@ -7475,29 +7491,29 @@
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J94" s="16" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K94" s="16" t="n">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="L94" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M94" s="16" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N94" s="17" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O94" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="17" t="n">
@@ -7507,30 +7523,32 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
-        </is>
-      </c>
-      <c r="E95" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -7540,34 +7558,34 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>964.1</v>
-      </c>
-      <c r="O95" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
@@ -7577,22 +7595,22 @@
     <row r="96">
       <c r="A96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="16" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E96" s="16" t="n">
@@ -7600,7 +7618,7 @@
       </c>
       <c r="F96" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G96" s="16" t="inlineStr">
@@ -7615,30 +7633,30 @@
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J96" s="16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K96" s="16" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L96" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M96" s="16" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N96" s="17" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="O96" s="14" t="n">
-        <v>70.2</v>
+        <v>0</v>
+      </c>
+      <c r="O96" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P96" s="17" t="n">
         <v>0</v>
@@ -7647,22 +7665,22 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E97" s="12" t="n">
@@ -7680,34 +7698,34 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O97" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="13" t="n">
@@ -7717,30 +7735,32 @@
     <row r="98">
       <c r="A98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="16" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
-        </is>
-      </c>
-      <c r="E98" s="16" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F98" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="16" t="inlineStr">
@@ -7750,34 +7770,34 @@
       </c>
       <c r="H98" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J98" s="16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K98" s="16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L98" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M98" s="16" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N98" s="17" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O98" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="17" t="n">
@@ -7787,22 +7807,22 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E99" s="12" t="n">
@@ -7825,29 +7845,29 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O99" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
@@ -7857,12 +7877,12 @@
     <row r="100">
       <c r="A100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C100" s="16" t="inlineStr">
@@ -7872,7 +7892,7 @@
       </c>
       <c r="D100" s="16" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E100" s="16" t="n">
@@ -7895,29 +7915,29 @@
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J100" s="16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K100" s="16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L100" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M100" s="16" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N100" s="17" t="n">
-        <v>250</v>
-      </c>
-      <c r="O100" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="17" t="n">
@@ -7927,12 +7947,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7942,7 +7962,7 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E101" s="12" t="n">
@@ -7965,29 +7985,29 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>460</v>
-      </c>
-      <c r="O101" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -7997,12 +8017,12 @@
     <row r="102">
       <c r="A102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C102" s="16" t="inlineStr">
@@ -8012,7 +8032,7 @@
       </c>
       <c r="D102" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E102" s="16" t="n">
@@ -8030,28 +8050,28 @@
       </c>
       <c r="H102" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J102" s="16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K102" s="16" t="n">
-        <v>0.25</v>
+        <v>0.62</v>
       </c>
       <c r="L102" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M102" s="16" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N102" s="17" t="n">
@@ -8067,12 +8087,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
@@ -8082,7 +8102,7 @@
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E103" s="12" t="n">
@@ -8105,23 +8125,23 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
@@ -8137,22 +8157,22 @@
     <row r="104">
       <c r="A104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E104" s="16" t="n">
@@ -8175,29 +8195,29 @@
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J104" s="16" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K104" s="16" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L104" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M104" s="16" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N104" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="17" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O104" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="17" t="n">
@@ -8207,22 +8227,22 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
@@ -8230,36 +8250,44 @@
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L105" s="12" t="inlineStr"/>
-      <c r="M105" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L105" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27493</t>
+        </is>
+      </c>
+      <c r="M105" s="12" t="inlineStr">
+        <is>
+          <t>495699</t>
+        </is>
+      </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>964.1</v>
+      </c>
+      <c r="O105" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8269,12 +8297,12 @@
     <row r="106">
       <c r="A106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C106" s="16" t="inlineStr">
@@ -8284,7 +8312,7 @@
       </c>
       <c r="D106" s="16" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E106" s="16" t="n">
@@ -8302,35 +8330,35 @@
       </c>
       <c r="H106" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J106" s="16" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M106" s="16" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N106" s="17" t="n">
-        <v>240</v>
+        <v>140.4</v>
       </c>
       <c r="O106" s="14" t="n">
-        <v>0</v>
+        <v>70.2</v>
       </c>
       <c r="P106" s="17" t="n">
         <v>0</v>
@@ -8339,12 +8367,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8354,7 +8382,7 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
@@ -8377,23 +8405,23 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8409,22 +8437,22 @@
     <row r="108">
       <c r="A108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D108" s="16" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E108" s="16" t="n">
@@ -8432,7 +8460,7 @@
       </c>
       <c r="F108" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G108" s="16" t="inlineStr">
@@ -8447,29 +8475,29 @@
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J108" s="16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K108" s="16" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L108" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M108" s="16" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N108" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="17" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O108" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="17" t="n">
@@ -8479,22 +8507,22 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
@@ -8502,32 +8530,40 @@
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L109" s="12" t="inlineStr"/>
-      <c r="M109" s="12" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L109" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M109" s="12" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N109" s="13" t="n">
         <v>0</v>
       </c>
@@ -8541,22 +8577,22 @@
     <row r="110">
       <c r="A110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C110" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="16" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E110" s="16" t="n">
@@ -8569,7 +8605,7 @@
       </c>
       <c r="G110" s="16" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="16" t="inlineStr">
@@ -8579,21 +8615,29 @@
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J110" s="16" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="K110" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L110" s="16" t="inlineStr"/>
-      <c r="M110" s="16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L110" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M110" s="16" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N110" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>250</v>
+      </c>
+      <c r="O110" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="17" t="n">
@@ -8603,22 +8647,22 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
@@ -8631,31 +8675,39 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L111" s="12" t="inlineStr"/>
-      <c r="M111" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L111" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M111" s="12" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N111" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O111" s="13" t="n">
+        <v>460</v>
+      </c>
+      <c r="O111" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
@@ -8665,12 +8717,12 @@
     <row r="112">
       <c r="A112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C112" s="16" t="inlineStr">
@@ -8680,7 +8732,7 @@
       </c>
       <c r="D112" s="16" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E112" s="16" t="n">
@@ -8703,23 +8755,23 @@
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J112" s="16" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K112" s="16" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M112" s="16" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N112" s="17" t="n">
@@ -8735,12 +8787,12 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8750,13 +8802,11 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8765,7 +8815,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H113" s="12" t="inlineStr">
@@ -8775,17 +8825,25 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="K113" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L113" s="12" t="inlineStr"/>
-      <c r="M113" s="12" t="inlineStr"/>
+      <c r="L113" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M113" s="12" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N113" s="13" t="n">
         <v>0</v>
       </c>
@@ -8799,12 +8857,12 @@
     <row r="114">
       <c r="A114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B114" s="16" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C114" s="16" t="inlineStr">
@@ -8814,13 +8872,11 @@
       </c>
       <c r="D114" s="16" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E114" s="16" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>COMMUNE D'ARCUEIL</t>
+        </is>
+      </c>
+      <c r="E114" s="16" t="n">
+        <v/>
       </c>
       <c r="F114" s="16" t="inlineStr">
         <is>
@@ -8829,27 +8885,35 @@
       </c>
       <c r="G114" s="16" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J114" s="16" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="K114" s="16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L114" s="16" t="inlineStr"/>
-      <c r="M114" s="16" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L114" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M114" s="16" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N114" s="17" t="n">
         <v>0</v>
       </c>
@@ -8863,24 +8927,26 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr"/>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E115" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>Biarritz</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v/>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
@@ -8899,14 +8965,14 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L115" s="12" t="inlineStr"/>
       <c r="M115" s="12" t="inlineStr"/>
@@ -8923,58 +8989,64 @@
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C116" s="16" t="inlineStr"/>
+          <t>[Besancon] Acquisition</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E116" s="16" t="inlineStr"/>
+          <t>Besançon</t>
+        </is>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v/>
+      </c>
       <c r="F116" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G116" s="16" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H116" s="16" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J116" s="16" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K116" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M116" s="16" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+          <t>PDMDEP-34437</t>
+        </is>
+      </c>
+      <c r="M116" s="16" t="inlineStr"/>
       <c r="N116" s="17" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O116" s="14" t="n">
-        <v>0</v>
+        <v>7375</v>
+      </c>
+      <c r="O116" s="17" t="n">
+        <v>7375</v>
       </c>
       <c r="P116" s="17" t="n">
         <v>0</v>
@@ -8983,89 +9055,865 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N117" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O117" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-18038</t>
+        </is>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v/>
+      </c>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H118" s="16" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J118" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="K118" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L118" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M118" s="16" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
+      <c r="N118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-18038</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>[CD 38] Reprise de 1644 AP</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J119" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K119" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L119" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
+      <c r="N119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-16868</t>
+        </is>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>[Limoges] migration placier</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>Limoges</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v/>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>26/09/2024</t>
+        </is>
+      </c>
+      <c r="J120" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="K120" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L120" s="16" t="inlineStr"/>
+      <c r="M120" s="16" t="inlineStr"/>
+      <c r="N120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-14551</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>[Perpignan] Interface formulaire</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>[Perpignan]</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>14/03/2024</t>
+        </is>
+      </c>
+      <c r="J121" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K121" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L121" s="12" t="inlineStr"/>
+      <c r="M121" s="12" t="inlineStr"/>
+      <c r="N121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-14254</t>
+        </is>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>Dijon métropole</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="n">
+        <v/>
+      </c>
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>19/02/2024</t>
+        </is>
+      </c>
+      <c r="J122" s="16" t="n">
+        <v>29</v>
+      </c>
+      <c r="K122" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L122" s="16" t="inlineStr"/>
+      <c r="M122" s="16" t="inlineStr"/>
+      <c r="N122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-14095</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>CC du Pays Sabolien</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F123" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H123" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>31/01/2024</t>
+        </is>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L123" s="12" t="inlineStr"/>
+      <c r="M123" s="12" t="inlineStr"/>
+      <c r="N123" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v/>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G124" s="16" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H124" s="16" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J124" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="K124" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-12241</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F125" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J125" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K125" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L125" s="12" t="inlineStr"/>
+      <c r="M125" s="12" t="inlineStr"/>
+      <c r="N125" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F126" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G126" s="16" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="16" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J126" s="16" t="n">
+        <v>34</v>
+      </c>
+      <c r="K126" s="16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L126" s="16" t="inlineStr"/>
+      <c r="M126" s="16" t="inlineStr"/>
+      <c r="N126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr"/>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F127" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J127" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K127" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L127" s="12" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
+      <c r="N127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="inlineStr"/>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr"/>
+      <c r="F128" s="16" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G128" s="16" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="inlineStr"/>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J128" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O128" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
           <t>PSC-1228</t>
         </is>
       </c>
-      <c r="B117" s="12" t="inlineStr">
+      <c r="B129" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="C117" s="12" t="inlineStr"/>
-      <c r="D117" s="12" t="inlineStr">
+      <c r="C129" s="12" t="inlineStr"/>
+      <c r="D129" s="12" t="inlineStr">
         <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E117" s="12" t="inlineStr"/>
-      <c r="F117" s="12" t="inlineStr">
+      <c r="E129" s="12" t="inlineStr"/>
+      <c r="F129" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G117" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr"/>
-      <c r="I117" s="12" t="inlineStr">
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr"/>
+      <c r="I129" s="12" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="12" t="inlineStr">
+      <c r="K129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M117" s="12" t="inlineStr">
+      <c r="M129" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N117" s="13" t="n">
+      <c r="N129" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O117" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="18" t="inlineStr">
+      <c r="O129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B118" s="18" t="inlineStr"/>
-      <c r="C118" s="18" t="inlineStr"/>
-      <c r="D118" s="18" t="inlineStr"/>
-      <c r="E118" s="18" t="inlineStr"/>
-      <c r="F118" s="18" t="inlineStr"/>
-      <c r="G118" s="18" t="inlineStr"/>
-      <c r="H118" s="18" t="inlineStr"/>
-      <c r="I118" s="18" t="inlineStr"/>
-      <c r="J118" s="18" t="inlineStr"/>
-      <c r="K118" s="18" t="inlineStr"/>
-      <c r="L118" s="18" t="inlineStr"/>
-      <c r="M118" s="18" t="inlineStr"/>
-      <c r="N118" s="19" t="n">
-        <v>60120.60999999999</v>
-      </c>
-      <c r="O118" s="19" t="n">
-        <v>6603.9</v>
-      </c>
-      <c r="P118" s="19" t="n">
-        <v>114.37</v>
+      <c r="B130" s="18" t="inlineStr"/>
+      <c r="C130" s="18" t="inlineStr"/>
+      <c r="D130" s="18" t="inlineStr"/>
+      <c r="E130" s="18" t="inlineStr"/>
+      <c r="F130" s="18" t="inlineStr"/>
+      <c r="G130" s="18" t="inlineStr"/>
+      <c r="H130" s="18" t="inlineStr"/>
+      <c r="I130" s="18" t="inlineStr"/>
+      <c r="J130" s="18" t="inlineStr"/>
+      <c r="K130" s="18" t="inlineStr"/>
+      <c r="L130" s="18" t="inlineStr"/>
+      <c r="M130" s="18" t="inlineStr"/>
+      <c r="N130" s="19" t="n">
+        <v>76075.26000000001</v>
+      </c>
+      <c r="O130" s="19" t="n">
+        <v>16606.3</v>
+      </c>
+      <c r="P130" s="19" t="n">
+        <v>262.63</v>
       </c>
     </row>
   </sheetData>
@@ -9184,6 +10032,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9758,16 +10618,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>34</v>
+        <v>34.75</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>43.75</v>
+        <v>45</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>8.75</v>
@@ -9777,7 +10637,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
     </row>
@@ -9788,7 +10648,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>11.5</v>
+        <v>15.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>2.5</v>
@@ -9797,17 +10657,17 @@
         <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>14</v>
+        <v>18.25</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.9%</t>
         </is>
       </c>
     </row>
@@ -9819,7 +10679,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>
@@ -9904,22 +10764,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>393984</v>
+        <v>411892</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>188364</v>
+        <v>203400</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>205620</v>
+        <v>208492</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172551</v>
+        <v>172452</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>17470</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>15599</v>
+        <v>18569</v>
       </c>
     </row>
     <row r="6">
@@ -9932,13 +10792,13 @@
         <v>186743</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>81797</v>
+        <v>81610</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>104945</v>
+        <v>105133</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>95727</v>
+        <v>95914</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4770</v>
@@ -9954,22 +10814,22 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>207241</v>
+        <v>225149</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>106567</v>
+        <v>121790</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>100675</v>
+        <v>103359</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>76824</v>
+        <v>76538</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>11151</v>
+        <v>14121</v>
       </c>
     </row>
   </sheetData>
@@ -10223,7 +11083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -10244,7 +11104,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2 clôture(s) : 2 projet(s), 0 rework</t>
+          <t>3 clôture(s) : 3 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -10284,22 +11144,22 @@
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-30241</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[MOLSHEIM] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>MOLSHEIM</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E5" s="16" t="inlineStr">
@@ -10308,65 +11168,95 @@
         </is>
       </c>
       <c r="F5" s="16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-31947</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
           <t>PDMDEP-33720</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="E7" s="16" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="28" t="n"/>
-      <c r="F9" s="28" t="n">
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-07-03.xlsx
+++ b/jira_export_2026-07-03.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>16,606 €</t>
+          <t>9,231 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>15,239 €</t>
+          <t>7,864 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>94 h</t>
+          <t>95 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P130"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -8832,7 +8832,7 @@
         <v>16</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
@@ -8989,12 +8989,12 @@
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C116" s="16" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D116" s="16" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E116" s="16" t="n">
@@ -9017,17 +9017,17 @@
       </c>
       <c r="G116" s="16" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H116" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J116" s="16" t="n">
@@ -9038,15 +9038,19 @@
       </c>
       <c r="L116" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34437</t>
-        </is>
-      </c>
-      <c r="M116" s="16" t="inlineStr"/>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M116" s="16" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N116" s="17" t="n">
-        <v>7375</v>
-      </c>
-      <c r="O116" s="17" t="n">
-        <v>7375</v>
+        <v>240</v>
+      </c>
+      <c r="O116" s="14" t="n">
+        <v>0</v>
       </c>
       <c r="P116" s="17" t="n">
         <v>0</v>
@@ -9055,22 +9059,22 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9078,7 +9082,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9088,34 +9092,34 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O117" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9140,7 +9144,7 @@
       </c>
       <c r="D118" s="16" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E118" s="16" t="n">
@@ -9174,7 +9178,7 @@
       </c>
       <c r="L118" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M118" s="16" t="inlineStr">
@@ -9195,22 +9199,22 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9218,40 +9222,32 @@
       </c>
       <c r="F119" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K119" s="12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L119" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M119" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L119" s="12" t="inlineStr"/>
+      <c r="M119" s="12" t="inlineStr"/>
       <c r="N119" s="13" t="n">
         <v>0</v>
       </c>
@@ -9265,22 +9261,22 @@
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E120" s="16" t="n">
@@ -9288,7 +9284,7 @@
       </c>
       <c r="F120" s="16" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G120" s="16" t="inlineStr">
@@ -9298,19 +9294,19 @@
       </c>
       <c r="H120" s="16" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J120" s="16" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K120" s="16" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L120" s="16" t="inlineStr"/>
       <c r="M120" s="16" t="inlineStr"/>
@@ -9327,12 +9323,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9342,7 +9338,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9365,14 +9361,14 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L121" s="12" t="inlineStr"/>
       <c r="M121" s="12" t="inlineStr"/>
@@ -9389,22 +9385,22 @@
     <row r="122">
       <c r="A122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E122" s="16" t="n">
@@ -9422,19 +9418,19 @@
       </c>
       <c r="H122" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J122" s="16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K122" s="16" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L122" s="16" t="inlineStr"/>
       <c r="M122" s="16" t="inlineStr"/>
@@ -9451,22 +9447,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9479,27 +9475,35 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L123" s="12" t="inlineStr"/>
-      <c r="M123" s="12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L123" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N123" s="13" t="n">
         <v>0</v>
       </c>
@@ -9513,12 +9517,12 @@
     <row r="124">
       <c r="A124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C124" s="16" t="inlineStr">
@@ -9528,11 +9532,13 @@
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="n">
-        <v/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
       </c>
       <c r="F124" s="16" t="inlineStr">
         <is>
@@ -9541,35 +9547,27 @@
       </c>
       <c r="G124" s="16" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J124" s="16" t="n">
         <v>34</v>
       </c>
       <c r="K124" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L124" s="16" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M124" s="16" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L124" s="16" t="inlineStr"/>
+      <c r="M124" s="16" t="inlineStr"/>
       <c r="N124" s="17" t="n">
         <v>0</v>
       </c>
@@ -9583,12 +9581,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9598,12 +9596,12 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Déploiement de Littéralis Expert</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -9618,7 +9616,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
@@ -9630,7 +9628,7 @@
         <v>34</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L125" s="12" t="inlineStr"/>
       <c r="M125" s="12" t="inlineStr"/>
@@ -9647,27 +9645,23 @@
     <row r="126">
       <c r="A126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr"/>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E126" s="16" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F126" s="16" t="inlineStr">
@@ -9682,19 +9676,19 @@
       </c>
       <c r="H126" s="16" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J126" s="16" t="n">
         <v>34</v>
       </c>
       <c r="K126" s="16" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="L126" s="16" t="inlineStr"/>
       <c r="M126" s="16" t="inlineStr"/>
@@ -9711,25 +9705,21 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr"/>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr"/>
       <c r="F127" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9737,31 +9727,35 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr"/>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L127" s="12" t="inlineStr"/>
-      <c r="M127" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L127" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O127" s="14" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9771,18 +9765,18 @@
     <row r="128">
       <c r="A128" s="15" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1228</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="C128" s="16" t="inlineStr"/>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
       <c r="E128" s="16" t="inlineStr"/>
@@ -9799,27 +9793,27 @@
       <c r="H128" s="16" t="inlineStr"/>
       <c r="I128" s="16" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="J128" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K128" s="16" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="16" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-32829</t>
         </is>
       </c>
       <c r="M128" s="16" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00163534</t>
         </is>
       </c>
       <c r="N128" s="17" t="n">
-        <v>510.6</v>
+        <v>50</v>
       </c>
       <c r="O128" s="14" t="n">
         <v>0</v>
@@ -9829,91 +9823,31 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="11" t="inlineStr">
-        <is>
-          <t>PSC-1228</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr"/>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr"/>
-      <c r="F129" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G129" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr"/>
-      <c r="I129" s="12" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="J129" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32829</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>00163534</t>
-        </is>
-      </c>
-      <c r="N129" s="13" t="n">
-        <v>50</v>
-      </c>
-      <c r="O129" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
+      <c r="A129" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B130" s="18" t="inlineStr"/>
-      <c r="C130" s="18" t="inlineStr"/>
-      <c r="D130" s="18" t="inlineStr"/>
-      <c r="E130" s="18" t="inlineStr"/>
-      <c r="F130" s="18" t="inlineStr"/>
-      <c r="G130" s="18" t="inlineStr"/>
-      <c r="H130" s="18" t="inlineStr"/>
-      <c r="I130" s="18" t="inlineStr"/>
-      <c r="J130" s="18" t="inlineStr"/>
-      <c r="K130" s="18" t="inlineStr"/>
-      <c r="L130" s="18" t="inlineStr"/>
-      <c r="M130" s="18" t="inlineStr"/>
-      <c r="N130" s="19" t="n">
-        <v>76075.26000000001</v>
-      </c>
-      <c r="O130" s="19" t="n">
-        <v>16606.3</v>
-      </c>
-      <c r="P130" s="19" t="n">
-        <v>262.63</v>
+      <c r="B129" s="18" t="inlineStr"/>
+      <c r="C129" s="18" t="inlineStr"/>
+      <c r="D129" s="18" t="inlineStr"/>
+      <c r="E129" s="18" t="inlineStr"/>
+      <c r="F129" s="18" t="inlineStr"/>
+      <c r="G129" s="18" t="inlineStr"/>
+      <c r="H129" s="18" t="inlineStr"/>
+      <c r="I129" s="18" t="inlineStr"/>
+      <c r="J129" s="18" t="inlineStr"/>
+      <c r="K129" s="18" t="inlineStr"/>
+      <c r="L129" s="18" t="inlineStr"/>
+      <c r="M129" s="18" t="inlineStr"/>
+      <c r="N129" s="19" t="n">
+        <v>68700.26000000001</v>
+      </c>
+      <c r="O129" s="19" t="n">
+        <v>9231.299999999999</v>
+      </c>
+      <c r="P129" s="19" t="n">
+        <v>143.72</v>
       </c>
     </row>
   </sheetData>
@@ -10043,7 +9977,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10618,16 +10551,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>34.75</v>
+        <v>35</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>9.5</v>
+        <v>10.25</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>8.75</v>
@@ -10637,7 +10570,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10612,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -10764,22 +10697,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>411892</v>
+        <v>397142</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>203400</v>
+        <v>188650</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>208492</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172452</v>
+        <v>172912</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>17470</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>18569</v>
+        <v>18109</v>
       </c>
     </row>
     <row r="6">
@@ -10798,13 +10731,13 @@
         <v>105133</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>95914</v>
+        <v>96374</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>4770</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>4448</v>
+        <v>3988</v>
       </c>
     </row>
     <row r="7">
@@ -10814,10 +10747,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>225149</v>
+        <v>210399</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>121790</v>
+        <v>107040</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>103359</v>

--- a/jira_export_2026-07-03.xlsx
+++ b/jira_export_2026-07-03.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>95 h</t>
+          <t>110 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -4918,7 +4918,7 @@
         <v>4</v>
       </c>
       <c r="K58" s="16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L58" s="16" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>8</v>
       </c>
       <c r="K98" s="16" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="L98" s="16" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>10</v>
       </c>
       <c r="K102" s="16" t="n">
-        <v>0.62</v>
+        <v>1.38</v>
       </c>
       <c r="L102" s="16" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         <v>10</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.62</v>
+        <v>1.38</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>34</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="L125" s="12" t="inlineStr"/>
       <c r="M125" s="12" t="inlineStr"/>
@@ -9847,7 +9847,7 @@
         <v>9231.299999999999</v>
       </c>
       <c r="P129" s="19" t="n">
-        <v>143.72</v>
+        <v>127.33</v>
       </c>
     </row>
   </sheetData>
@@ -10551,26 +10551,26 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>35</v>
+        <v>40.75</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>10.25</v>
+        <v>12.75</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>46</v>
+        <v>54.25</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>8.75</v>
+        <v>13.75</v>
       </c>
       <c r="G5" s="16" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-03.xlsx
+++ b/jira_export_2026-07-03.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>110 h</t>
+          <t>116 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:P130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -2478,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L24" s="16" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>8</v>
       </c>
       <c r="K90" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L90" s="16" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>8</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         <v>8</v>
       </c>
       <c r="K92" s="16" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="L92" s="16" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>8</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>8</v>
       </c>
       <c r="K94" s="16" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="L94" s="16" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>8</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>9</v>
       </c>
       <c r="K100" s="16" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L100" s="16" t="inlineStr">
         <is>
@@ -9261,22 +9261,22 @@
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B120" s="16" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C120" s="16" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="16" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E120" s="16" t="n">
@@ -9299,14 +9299,14 @@
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J120" s="16" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K120" s="16" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L120" s="16" t="inlineStr"/>
       <c r="M120" s="16" t="inlineStr"/>
@@ -9323,12 +9323,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9361,14 +9361,14 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L121" s="12" t="inlineStr"/>
       <c r="M121" s="12" t="inlineStr"/>
@@ -9385,22 +9385,22 @@
     <row r="122">
       <c r="A122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C122" s="16" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="16" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E122" s="16" t="n">
@@ -9418,16 +9418,16 @@
       </c>
       <c r="H122" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J122" s="16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K122" s="16" t="n">
         <v>0.75</v>
@@ -9447,22 +9447,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9475,35 +9475,27 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L123" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M123" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L123" s="12" t="inlineStr"/>
+      <c r="M123" s="12" t="inlineStr"/>
       <c r="N123" s="13" t="n">
         <v>0</v>
       </c>
@@ -9517,12 +9509,12 @@
     <row r="124">
       <c r="A124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B124" s="16" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C124" s="16" t="inlineStr">
@@ -9532,13 +9524,11 @@
       </c>
       <c r="D124" s="16" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E124" s="16" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v/>
       </c>
       <c r="F124" s="16" t="inlineStr">
         <is>
@@ -9547,27 +9537,35 @@
       </c>
       <c r="G124" s="16" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J124" s="16" t="n">
         <v>34</v>
       </c>
       <c r="K124" s="16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L124" s="16" t="inlineStr"/>
-      <c r="M124" s="16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L124" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M124" s="16" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N124" s="17" t="n">
         <v>0</v>
       </c>
@@ -9581,12 +9579,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9596,12 +9594,12 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E125" s="12" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -9616,7 +9614,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
@@ -9628,7 +9626,7 @@
         <v>34</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="L125" s="12" t="inlineStr"/>
       <c r="M125" s="12" t="inlineStr"/>
@@ -9645,23 +9643,27 @@
     <row r="126">
       <c r="A126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B126" s="16" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D126" s="16" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E126" s="16" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F126" s="16" t="inlineStr">
@@ -9676,19 +9678,19 @@
       </c>
       <c r="H126" s="16" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J126" s="16" t="n">
         <v>34</v>
       </c>
       <c r="K126" s="16" t="n">
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="L126" s="16" t="inlineStr"/>
       <c r="M126" s="16" t="inlineStr"/>
@@ -9705,21 +9707,25 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr"/>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E127" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -9727,35 +9733,31 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H127" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M127" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>1.75</v>
+      </c>
+      <c r="L127" s="12" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr"/>
       <c r="N127" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O127" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9765,18 +9767,18 @@
     <row r="128">
       <c r="A128" s="15" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B128" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C128" s="16" t="inlineStr"/>
       <c r="D128" s="16" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E128" s="16" t="inlineStr"/>
@@ -9793,61 +9795,121 @@
       <c r="H128" s="16" t="inlineStr"/>
       <c r="I128" s="16" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J128" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M128" s="16" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N128" s="17" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O128" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1228</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr"/>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="inlineStr"/>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr"/>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J128" s="16" t="n">
+      <c r="J129" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K128" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="16" t="inlineStr">
+      <c r="K129" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M128" s="16" t="inlineStr">
+      <c r="M129" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N128" s="17" t="n">
+      <c r="N129" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O128" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="18" t="inlineStr">
+      <c r="O129" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B129" s="18" t="inlineStr"/>
-      <c r="C129" s="18" t="inlineStr"/>
-      <c r="D129" s="18" t="inlineStr"/>
-      <c r="E129" s="18" t="inlineStr"/>
-      <c r="F129" s="18" t="inlineStr"/>
-      <c r="G129" s="18" t="inlineStr"/>
-      <c r="H129" s="18" t="inlineStr"/>
-      <c r="I129" s="18" t="inlineStr"/>
-      <c r="J129" s="18" t="inlineStr"/>
-      <c r="K129" s="18" t="inlineStr"/>
-      <c r="L129" s="18" t="inlineStr"/>
-      <c r="M129" s="18" t="inlineStr"/>
-      <c r="N129" s="19" t="n">
+      <c r="B130" s="18" t="inlineStr"/>
+      <c r="C130" s="18" t="inlineStr"/>
+      <c r="D130" s="18" t="inlineStr"/>
+      <c r="E130" s="18" t="inlineStr"/>
+      <c r="F130" s="18" t="inlineStr"/>
+      <c r="G130" s="18" t="inlineStr"/>
+      <c r="H130" s="18" t="inlineStr"/>
+      <c r="I130" s="18" t="inlineStr"/>
+      <c r="J130" s="18" t="inlineStr"/>
+      <c r="K130" s="18" t="inlineStr"/>
+      <c r="L130" s="18" t="inlineStr"/>
+      <c r="M130" s="18" t="inlineStr"/>
+      <c r="N130" s="19" t="n">
         <v>68700.26000000001</v>
       </c>
-      <c r="O129" s="19" t="n">
+      <c r="O130" s="19" t="n">
         <v>9231.299999999999</v>
       </c>
-      <c r="P129" s="19" t="n">
-        <v>127.33</v>
+      <c r="P130" s="19" t="n">
+        <v>123.91</v>
       </c>
     </row>
   </sheetData>
@@ -9977,6 +10039,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId123"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId125"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10551,16 +10614,16 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>40.75</v>
+        <v>42.5</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>54.25</v>
+        <v>56.25</v>
       </c>
       <c r="F5" s="16" t="n">
         <v>13.75</v>
@@ -10570,7 +10633,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10675,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>18.5</v>
+        <v>22.75</v>
       </c>
     </row>
   </sheetData>
@@ -10700,13 +10763,13 @@
         <v>397142</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>188650</v>
+        <v>192427</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>208492</v>
+        <v>204715</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>172912</v>
+        <v>169136</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>17470</v>
@@ -10750,13 +10813,13 @@
         <v>210399</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>107040</v>
+        <v>110817</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>103359</v>
+        <v>99582</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>76538</v>
+        <v>72761</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
